--- a/data/gravel/Awson Gravel ART 2025.xlsx
+++ b/data/gravel/Awson Gravel ART 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2175975-1B29-6F43-A981-48DBFBE58F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18052C2-6037-E84C-89BE-938A75B1281E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="1400" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -350,10 +350,10 @@
     <t>integrated</t>
   </si>
   <si>
-    <t>spec'd tire size</t>
-  </si>
-  <si>
     <t>a8:g32</t>
+  </si>
+  <si>
+    <t>intagram message</t>
   </si>
 </sst>
 </file>
@@ -775,7 +775,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -1287,19 +1287,19 @@
         <v>27</v>
       </c>
       <c r="C30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G30">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -1370,10 +1370,10 @@
         <v>35</v>
       </c>
       <c r="B41">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
